--- a/data/raw/GLNPO 2024 Spring/Erie/D100/ER 91M D100 Spring 2024 24GE03I73 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Erie/D100/ER 91M D100 Spring 2024 24GE03I73 Zoop.xlsx
@@ -5,22 +5,22 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\GLNPO 2024 Spring\Erie\D100\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Erie\D100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1CECC90-B3A6-40FB-879C-505727908EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C4E39C3-D601-4FB0-BB35-0FBCBCD79B68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{93838704-6B7F-4795-9885-9CFF1C53C5A9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{93838704-6B7F-4795-9885-9CFF1C53C5A9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$379</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$378</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="16" r:id="rId2"/>
+    <pivotCache cacheId="7" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -573,7 +573,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -608,7 +608,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8269,7 +8268,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0C61590B-2C13-4E11-B273-430C35076059}" name="PivotTable1" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0C61590B-2C13-4E11-B273-430C35076059}" name="PivotTable1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="U2:Z24" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField showAll="0"/>
@@ -8744,19 +8743,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B91CC818-BA2C-4EF6-B0DA-8A77882ECDA0}">
   <dimension ref="A1:Z379"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="31.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="31.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="31.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="31.88671875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.88671875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="4" bestFit="1" customWidth="1"/>
     <col min="24" max="25" width="3" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8812,7 +8811,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -8871,7 +8870,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -8942,7 +8941,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -8997,21 +8996,20 @@
       <c r="U4" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="V4" s="20">
-        <v>1</v>
-      </c>
-      <c r="W4" s="20">
+      <c r="V4">
+        <v>1</v>
+      </c>
+      <c r="W4">
         <v>0</v>
       </c>
-      <c r="X4" s="20">
+      <c r="X4">
         <v>0</v>
       </c>
-      <c r="Y4" s="20"/>
-      <c r="Z4" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Z4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -9066,21 +9064,20 @@
       <c r="U5" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="V5" s="20">
+      <c r="V5">
         <v>7</v>
       </c>
-      <c r="W5" s="20">
+      <c r="W5">
         <v>10</v>
       </c>
-      <c r="X5" s="20">
+      <c r="X5">
         <v>33</v>
       </c>
-      <c r="Y5" s="20"/>
-      <c r="Z5" s="20">
+      <c r="Z5">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -9135,19 +9132,17 @@
       <c r="U6" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="V6" s="20">
+      <c r="V6">
         <v>31</v>
       </c>
-      <c r="W6" s="20">
+      <c r="W6">
         <v>31</v>
       </c>
-      <c r="X6" s="20"/>
-      <c r="Y6" s="20"/>
-      <c r="Z6" s="20">
+      <c r="Z6">
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -9202,21 +9197,20 @@
       <c r="U7" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="V7" s="20">
+      <c r="V7">
         <v>14</v>
       </c>
-      <c r="W7" s="20">
+      <c r="W7">
         <v>15</v>
       </c>
-      <c r="X7" s="20">
-        <v>20</v>
-      </c>
-      <c r="Y7" s="20"/>
-      <c r="Z7" s="20">
+      <c r="X7">
+        <v>20</v>
+      </c>
+      <c r="Z7">
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -9271,21 +9265,20 @@
       <c r="U8" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="V8" s="20">
-        <v>1</v>
-      </c>
-      <c r="W8" s="20">
+      <c r="V8">
+        <v>1</v>
+      </c>
+      <c r="W8">
         <v>0</v>
       </c>
-      <c r="X8" s="20">
+      <c r="X8">
         <v>0</v>
       </c>
-      <c r="Y8" s="20"/>
-      <c r="Z8" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Z8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -9340,21 +9333,20 @@
       <c r="U9" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="V9" s="20">
+      <c r="V9">
         <v>3</v>
       </c>
-      <c r="W9" s="20">
+      <c r="W9">
         <v>3</v>
       </c>
-      <c r="X9" s="20">
+      <c r="X9">
         <v>4</v>
       </c>
-      <c r="Y9" s="20"/>
-      <c r="Z9" s="20">
+      <c r="Z9">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -9409,19 +9401,17 @@
       <c r="U10" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="V10" s="20">
+      <c r="V10">
         <v>76</v>
       </c>
-      <c r="W10" s="20">
+      <c r="W10">
         <v>82</v>
       </c>
-      <c r="X10" s="20"/>
-      <c r="Y10" s="20"/>
-      <c r="Z10" s="20">
+      <c r="Z10">
         <v>158</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -9476,19 +9466,17 @@
       <c r="U11" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="V11" s="20">
-        <v>22</v>
-      </c>
-      <c r="W11" s="20">
-        <v>23</v>
-      </c>
-      <c r="X11" s="20"/>
-      <c r="Y11" s="20"/>
-      <c r="Z11" s="20">
+      <c r="V11">
+        <v>22</v>
+      </c>
+      <c r="W11">
+        <v>23</v>
+      </c>
+      <c r="Z11">
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -9543,21 +9531,20 @@
       <c r="U12" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="V12" s="20">
+      <c r="V12">
         <v>0</v>
       </c>
-      <c r="W12" s="20">
-        <v>1</v>
-      </c>
-      <c r="X12" s="20">
+      <c r="W12">
+        <v>1</v>
+      </c>
+      <c r="X12">
         <v>0</v>
       </c>
-      <c r="Y12" s="20"/>
-      <c r="Z12" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Z12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -9612,19 +9599,17 @@
       <c r="U13" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="V13" s="20">
+      <c r="V13">
         <v>59</v>
       </c>
-      <c r="W13" s="20">
-        <v>34</v>
-      </c>
-      <c r="X13" s="20"/>
-      <c r="Y13" s="20"/>
-      <c r="Z13" s="20">
+      <c r="W13">
+        <v>34</v>
+      </c>
+      <c r="Z13">
         <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -9679,19 +9664,17 @@
       <c r="U14" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="V14" s="20">
+      <c r="V14">
         <v>56</v>
       </c>
-      <c r="W14" s="20">
+      <c r="W14">
         <v>77</v>
       </c>
-      <c r="X14" s="20"/>
-      <c r="Y14" s="20"/>
-      <c r="Z14" s="20">
+      <c r="Z14">
         <v>133</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -9746,21 +9729,20 @@
       <c r="U15" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="V15" s="20">
+      <c r="V15">
         <v>11</v>
       </c>
-      <c r="W15" s="20">
+      <c r="W15">
         <v>4</v>
       </c>
-      <c r="X15" s="20">
+      <c r="X15">
         <v>11</v>
       </c>
-      <c r="Y15" s="20"/>
-      <c r="Z15" s="20">
+      <c r="Z15">
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -9815,23 +9797,23 @@
       <c r="U16" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="V16" s="20">
+      <c r="V16">
         <v>2</v>
       </c>
-      <c r="W16" s="20">
+      <c r="W16">
         <v>0</v>
       </c>
-      <c r="X16" s="20">
+      <c r="X16">
         <v>3</v>
       </c>
-      <c r="Y16" s="20">
+      <c r="Y16">
         <v>2</v>
       </c>
-      <c r="Z16" s="20">
+      <c r="Z16">
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -9886,21 +9868,20 @@
       <c r="U17" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="V17" s="20">
+      <c r="V17">
         <v>6</v>
       </c>
-      <c r="W17" s="20">
+      <c r="W17">
         <v>4</v>
       </c>
-      <c r="X17" s="20">
+      <c r="X17">
         <v>3</v>
       </c>
-      <c r="Y17" s="20"/>
-      <c r="Z17" s="20">
+      <c r="Z17">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -9955,23 +9936,23 @@
       <c r="U18" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="V18" s="20">
-        <v>1</v>
-      </c>
-      <c r="W18" s="20">
+      <c r="V18">
+        <v>1</v>
+      </c>
+      <c r="W18">
         <v>0</v>
       </c>
-      <c r="X18" s="20">
+      <c r="X18">
         <v>4</v>
       </c>
-      <c r="Y18" s="20">
+      <c r="Y18">
         <v>8</v>
       </c>
-      <c r="Z18" s="20">
+      <c r="Z18">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -10026,21 +10007,20 @@
       <c r="U19" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="V19" s="20">
+      <c r="V19">
         <v>5</v>
       </c>
-      <c r="W19" s="20">
+      <c r="W19">
         <v>3</v>
       </c>
-      <c r="X19" s="20">
+      <c r="X19">
         <v>5</v>
       </c>
-      <c r="Y19" s="20"/>
-      <c r="Z19" s="20">
+      <c r="Z19">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -10095,21 +10075,20 @@
       <c r="U20" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="V20" s="20">
+      <c r="V20">
         <v>2</v>
       </c>
-      <c r="W20" s="20">
-        <v>1</v>
-      </c>
-      <c r="X20" s="20">
+      <c r="W20">
+        <v>1</v>
+      </c>
+      <c r="X20">
         <v>4</v>
       </c>
-      <c r="Y20" s="20"/>
-      <c r="Z20" s="20">
+      <c r="Z20">
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -10164,23 +10143,23 @@
       <c r="U21" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="V21" s="20">
+      <c r="V21">
         <v>0</v>
       </c>
-      <c r="W21" s="20">
+      <c r="W21">
         <v>0</v>
       </c>
-      <c r="X21" s="20">
+      <c r="X21">
         <v>0</v>
       </c>
-      <c r="Y21" s="20">
-        <v>1</v>
-      </c>
-      <c r="Z21" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y21">
+        <v>1</v>
+      </c>
+      <c r="Z21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -10235,21 +10214,20 @@
       <c r="U22" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="V22" s="20">
+      <c r="V22">
         <v>11</v>
       </c>
-      <c r="W22" s="20">
+      <c r="W22">
         <v>7</v>
       </c>
-      <c r="X22" s="20">
+      <c r="X22">
         <v>5</v>
       </c>
-      <c r="Y22" s="20"/>
-      <c r="Z22" s="20">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Z22">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -10304,21 +10282,20 @@
       <c r="U23" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="V23" s="20">
-        <v>1</v>
-      </c>
-      <c r="W23" s="20">
+      <c r="V23">
+        <v>1</v>
+      </c>
+      <c r="W23">
         <v>0</v>
       </c>
-      <c r="X23" s="20">
+      <c r="X23">
         <v>0</v>
       </c>
-      <c r="Y23" s="20"/>
-      <c r="Z23" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Z23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -10373,23 +10350,23 @@
       <c r="U24" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="V24" s="20">
+      <c r="V24">
         <v>309</v>
       </c>
-      <c r="W24" s="20">
+      <c r="W24">
         <v>295</v>
       </c>
-      <c r="X24" s="20">
+      <c r="X24">
         <v>92</v>
       </c>
-      <c r="Y24" s="20">
+      <c r="Y24">
         <v>11</v>
       </c>
-      <c r="Z24" s="20">
+      <c r="Z24">
         <v>707</v>
       </c>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -10442,7 +10419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -10504,7 +10481,7 @@
         <v>0.995</v>
       </c>
     </row>
-    <row r="27" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -10564,7 +10541,7 @@
         <v>1.0029999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -10626,7 +10603,7 @@
         <v>0.998</v>
       </c>
     </row>
-    <row r="29" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -10686,7 +10663,7 @@
         <v>1.002</v>
       </c>
     </row>
-    <row r="30" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -10746,7 +10723,7 @@
       </c>
       <c r="W30" s="19"/>
     </row>
-    <row r="31" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -10806,7 +10783,7 @@
       </c>
       <c r="W31" s="19"/>
     </row>
-    <row r="32" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -10864,7 +10841,7 @@
       <c r="V32" s="18"/>
       <c r="W32" s="19"/>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -10917,7 +10894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -10970,7 +10947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -11023,7 +11000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -11076,7 +11053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -11129,7 +11106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -11182,7 +11159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -11235,7 +11212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -11288,7 +11265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -11341,7 +11318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -11394,7 +11371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -11447,7 +11424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -11500,7 +11477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -11553,7 +11530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -11606,7 +11583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -11659,7 +11636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -11712,7 +11689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -11765,7 +11742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -11818,7 +11795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -11871,7 +11848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -11924,7 +11901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -11977,7 +11954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -12030,7 +12007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -12083,7 +12060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -12136,7 +12113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -12189,7 +12166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -12242,7 +12219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -12295,7 +12272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -12348,7 +12325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -12401,7 +12378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -12454,7 +12431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -12507,7 +12484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -12560,7 +12537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>18</v>
       </c>
@@ -12613,7 +12590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -12666,7 +12643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -12719,7 +12696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -12772,7 +12749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -12825,7 +12802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -12878,7 +12855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -12931,7 +12908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -12984,7 +12961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -13037,7 +13014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -13090,7 +13067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -13143,7 +13120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -13196,7 +13173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>18</v>
       </c>
@@ -13249,7 +13226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -13302,7 +13279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -13355,7 +13332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>18</v>
       </c>
@@ -13408,7 +13385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -13461,7 +13438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>18</v>
       </c>
@@ -13514,7 +13491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>18</v>
       </c>
@@ -13567,7 +13544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>18</v>
       </c>
@@ -13620,7 +13597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>18</v>
       </c>
@@ -13673,7 +13650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>18</v>
       </c>
@@ -13726,7 +13703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>18</v>
       </c>
@@ -13779,7 +13756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>18</v>
       </c>
@@ -13832,7 +13809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>18</v>
       </c>
@@ -13885,7 +13862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>18</v>
       </c>
@@ -13938,7 +13915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>18</v>
       </c>
@@ -13991,7 +13968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>18</v>
       </c>
@@ -14044,7 +14021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>18</v>
       </c>
@@ -14097,7 +14074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>18</v>
       </c>
@@ -14150,7 +14127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>18</v>
       </c>
@@ -14203,7 +14180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>18</v>
       </c>
@@ -14256,7 +14233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>18</v>
       </c>
@@ -14309,7 +14286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>18</v>
       </c>
@@ -14362,7 +14339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -14415,7 +14392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>18</v>
       </c>
@@ -14468,7 +14445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>18</v>
       </c>
@@ -14521,7 +14498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>18</v>
       </c>
@@ -14574,7 +14551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>18</v>
       </c>
@@ -14627,7 +14604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>18</v>
       </c>
@@ -14680,7 +14657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>18</v>
       </c>
@@ -14733,7 +14710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>18</v>
       </c>
@@ -14786,7 +14763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>18</v>
       </c>
@@ -14839,7 +14816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>18</v>
       </c>
@@ -14892,7 +14869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>18</v>
       </c>
@@ -14933,7 +14910,7 @@
         <v>56</v>
       </c>
       <c r="N109" s="4" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="O109">
         <v>1.212</v>
@@ -14945,7 +14922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>18</v>
       </c>
@@ -14998,7 +14975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -15051,7 +15028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>18</v>
       </c>
@@ -15104,7 +15081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>18</v>
       </c>
@@ -15157,7 +15134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>18</v>
       </c>
@@ -15213,7 +15190,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>18</v>
       </c>
@@ -15266,7 +15243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>18</v>
       </c>
@@ -15319,7 +15296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>18</v>
       </c>
@@ -15372,7 +15349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>18</v>
       </c>
@@ -15425,7 +15402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>18</v>
       </c>
@@ -15478,7 +15455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>18</v>
       </c>
@@ -15531,7 +15508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>18</v>
       </c>
@@ -15584,7 +15561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>18</v>
       </c>
@@ -15637,7 +15614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>18</v>
       </c>
@@ -15690,7 +15667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -15743,7 +15720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>18</v>
       </c>
@@ -15796,7 +15773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>18</v>
       </c>
@@ -15849,7 +15826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>18</v>
       </c>
@@ -15902,7 +15879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>18</v>
       </c>
@@ -15955,7 +15932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>18</v>
       </c>
@@ -16008,7 +15985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>18</v>
       </c>
@@ -16061,7 +16038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>18</v>
       </c>
@@ -16114,7 +16091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>18</v>
       </c>
@@ -16167,7 +16144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>18</v>
       </c>
@@ -16220,7 +16197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>18</v>
       </c>
@@ -16273,7 +16250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>18</v>
       </c>
@@ -16326,7 +16303,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>18</v>
       </c>
@@ -16379,7 +16356,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>18</v>
       </c>
@@ -16432,7 +16409,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>18</v>
       </c>
@@ -16485,7 +16462,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>18</v>
       </c>
@@ -16538,7 +16515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>18</v>
       </c>
@@ -16591,7 +16568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>18</v>
       </c>
@@ -16644,7 +16621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>18</v>
       </c>
@@ -16697,7 +16674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>18</v>
       </c>
@@ -16750,7 +16727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -16803,7 +16780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>18</v>
       </c>
@@ -16856,7 +16833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>18</v>
       </c>
@@ -16909,7 +16886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>18</v>
       </c>
@@ -16962,7 +16939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>18</v>
       </c>
@@ -17015,7 +16992,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>18</v>
       </c>
@@ -17068,7 +17045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>18</v>
       </c>
@@ -17121,7 +17098,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>18</v>
       </c>
@@ -17174,7 +17151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>18</v>
       </c>
@@ -17227,7 +17204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>18</v>
       </c>
@@ -17280,7 +17257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>18</v>
       </c>
@@ -17333,7 +17310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>18</v>
       </c>
@@ -17386,7 +17363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>18</v>
       </c>
@@ -17439,7 +17416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>18</v>
       </c>
@@ -17492,7 +17469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>18</v>
       </c>
@@ -17545,7 +17522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>18</v>
       </c>
@@ -17598,7 +17575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>18</v>
       </c>
@@ -17651,7 +17628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>18</v>
       </c>
@@ -17704,7 +17681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>18</v>
       </c>
@@ -17757,7 +17734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>18</v>
       </c>
@@ -17810,7 +17787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>18</v>
       </c>
@@ -17863,7 +17840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>18</v>
       </c>
@@ -17916,7 +17893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>18</v>
       </c>
@@ -17969,7 +17946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>18</v>
       </c>
@@ -18022,7 +17999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>18</v>
       </c>
@@ -18075,7 +18052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>18</v>
       </c>
@@ -18128,7 +18105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>18</v>
       </c>
@@ -18181,7 +18158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>18</v>
       </c>
@@ -18234,7 +18211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>18</v>
       </c>
@@ -18287,7 +18264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>18</v>
       </c>
@@ -18340,7 +18317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>18</v>
       </c>
@@ -18393,7 +18370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>18</v>
       </c>
@@ -18446,7 +18423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>18</v>
       </c>
@@ -18499,7 +18476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>18</v>
       </c>
@@ -18552,7 +18529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>18</v>
       </c>
@@ -18605,7 +18582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>18</v>
       </c>
@@ -18658,7 +18635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>18</v>
       </c>
@@ -18711,7 +18688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>18</v>
       </c>
@@ -18764,7 +18741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>18</v>
       </c>
@@ -18817,7 +18794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>18</v>
       </c>
@@ -18870,7 +18847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>18</v>
       </c>
@@ -18923,7 +18900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>18</v>
       </c>
@@ -18976,7 +18953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>18</v>
       </c>
@@ -19029,7 +19006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>18</v>
       </c>
@@ -19082,7 +19059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>18</v>
       </c>
@@ -19135,7 +19112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>18</v>
       </c>
@@ -19188,7 +19165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>18</v>
       </c>
@@ -19241,7 +19218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>18</v>
       </c>
@@ -19294,7 +19271,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>18</v>
       </c>
@@ -19347,7 +19324,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>18</v>
       </c>
@@ -19400,7 +19377,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>18</v>
       </c>
@@ -19453,7 +19430,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>18</v>
       </c>
@@ -19506,7 +19483,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>18</v>
       </c>
@@ -19559,7 +19536,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>18</v>
       </c>
@@ -19612,7 +19589,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>18</v>
       </c>
@@ -19665,7 +19642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>18</v>
       </c>
@@ -19718,7 +19695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>18</v>
       </c>
@@ -19771,7 +19748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>18</v>
       </c>
@@ -19824,7 +19801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>18</v>
       </c>
@@ -19877,7 +19854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>18</v>
       </c>
@@ -19930,7 +19907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>18</v>
       </c>
@@ -19983,7 +19960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>18</v>
       </c>
@@ -20036,7 +20013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>18</v>
       </c>
@@ -20089,7 +20066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>18</v>
       </c>
@@ -20142,7 +20119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>18</v>
       </c>
@@ -20195,7 +20172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>18</v>
       </c>
@@ -20248,7 +20225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>18</v>
       </c>
@@ -20301,7 +20278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>18</v>
       </c>
@@ -20354,7 +20331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>18</v>
       </c>
@@ -20407,7 +20384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>18</v>
       </c>
@@ -20460,7 +20437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>18</v>
       </c>
@@ -20513,7 +20490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>18</v>
       </c>
@@ -20566,7 +20543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>18</v>
       </c>
@@ -20619,7 +20596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>18</v>
       </c>
@@ -20672,7 +20649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>18</v>
       </c>
@@ -20725,7 +20702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>18</v>
       </c>
@@ -20778,7 +20755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>18</v>
       </c>
@@ -20831,7 +20808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>18</v>
       </c>
@@ -20884,7 +20861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>18</v>
       </c>
@@ -20937,7 +20914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>18</v>
       </c>
@@ -20990,7 +20967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>18</v>
       </c>
@@ -21043,7 +21020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>18</v>
       </c>
@@ -21096,7 +21073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>18</v>
       </c>
@@ -21149,7 +21126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>18</v>
       </c>
@@ -21202,7 +21179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>18</v>
       </c>
@@ -21255,7 +21232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>18</v>
       </c>
@@ -21308,7 +21285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>18</v>
       </c>
@@ -21361,7 +21338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>18</v>
       </c>
@@ -21414,7 +21391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>18</v>
       </c>
@@ -21467,7 +21444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>18</v>
       </c>
@@ -21520,7 +21497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>18</v>
       </c>
@@ -21573,7 +21550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>18</v>
       </c>
@@ -21626,7 +21603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>18</v>
       </c>
@@ -21679,7 +21656,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="237" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>18</v>
       </c>
@@ -21732,7 +21709,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="238" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>18</v>
       </c>
@@ -21785,7 +21762,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="239" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>18</v>
       </c>
@@ -21838,7 +21815,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="240" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>18</v>
       </c>
@@ -21891,7 +21868,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="241" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>18</v>
       </c>
@@ -21944,7 +21921,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="242" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>18</v>
       </c>
@@ -21997,7 +21974,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="243" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>18</v>
       </c>
@@ -22050,7 +22027,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="244" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>18</v>
       </c>
@@ -22103,7 +22080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>18</v>
       </c>
@@ -22156,7 +22133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>18</v>
       </c>
@@ -22209,7 +22186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>18</v>
       </c>
@@ -22262,7 +22239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>18</v>
       </c>
@@ -22315,7 +22292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>18</v>
       </c>
@@ -22368,7 +22345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>18</v>
       </c>
@@ -22421,7 +22398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>18</v>
       </c>
@@ -22474,7 +22451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>18</v>
       </c>
@@ -22527,7 +22504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>18</v>
       </c>
@@ -22583,7 +22560,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="254" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>18</v>
       </c>
@@ -22636,7 +22613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>18</v>
       </c>
@@ -22689,7 +22666,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="256" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>18</v>
       </c>
@@ -22742,7 +22719,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="257" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>18</v>
       </c>
@@ -22795,7 +22772,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="258" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>18</v>
       </c>
@@ -22848,7 +22825,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="259" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>18</v>
       </c>
@@ -22901,7 +22878,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="260" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>18</v>
       </c>
@@ -22954,7 +22931,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="261" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>18</v>
       </c>
@@ -23007,7 +22984,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="262" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>18</v>
       </c>
@@ -23060,7 +23037,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="263" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>18</v>
       </c>
@@ -23113,7 +23090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>18</v>
       </c>
@@ -23166,7 +23143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>18</v>
       </c>
@@ -23219,7 +23196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>18</v>
       </c>
@@ -23272,7 +23249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>18</v>
       </c>
@@ -23325,7 +23302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>18</v>
       </c>
@@ -23378,7 +23355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>18</v>
       </c>
@@ -23431,7 +23408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>18</v>
       </c>
@@ -23484,7 +23461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>18</v>
       </c>
@@ -23537,7 +23514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>18</v>
       </c>
@@ -23590,7 +23567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>18</v>
       </c>
@@ -23643,7 +23620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>18</v>
       </c>
@@ -23696,7 +23673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>18</v>
       </c>
@@ -23749,7 +23726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>18</v>
       </c>
@@ -23802,7 +23779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>18</v>
       </c>
@@ -23855,7 +23832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>18</v>
       </c>
@@ -23908,7 +23885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>18</v>
       </c>
@@ -23961,7 +23938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>18</v>
       </c>
@@ -24014,7 +23991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>18</v>
       </c>
@@ -24067,7 +24044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>18</v>
       </c>
@@ -24120,7 +24097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>18</v>
       </c>
@@ -24176,7 +24153,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="284" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>18</v>
       </c>
@@ -24229,7 +24206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>18</v>
       </c>
@@ -24282,7 +24259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>18</v>
       </c>
@@ -24335,7 +24312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>18</v>
       </c>
@@ -24388,7 +24365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>18</v>
       </c>
@@ -24441,7 +24418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>18</v>
       </c>
@@ -24494,7 +24471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>18</v>
       </c>
@@ -24547,7 +24524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>18</v>
       </c>
@@ -24600,7 +24577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="292" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>18</v>
       </c>
@@ -24653,7 +24630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>18</v>
       </c>
@@ -24706,7 +24683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>18</v>
       </c>
@@ -24759,7 +24736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>18</v>
       </c>
@@ -24812,7 +24789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>18</v>
       </c>
@@ -24865,7 +24842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>18</v>
       </c>
@@ -24918,7 +24895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="298" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>18</v>
       </c>
@@ -24971,7 +24948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="299" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>18</v>
       </c>
@@ -25024,7 +25001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="300" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>18</v>
       </c>
@@ -25077,7 +25054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="301" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>18</v>
       </c>
@@ -25130,7 +25107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>18</v>
       </c>
@@ -25183,7 +25160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>18</v>
       </c>
@@ -25236,7 +25213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>18</v>
       </c>
@@ -25289,7 +25266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="305" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>18</v>
       </c>
@@ -25342,7 +25319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>18</v>
       </c>
@@ -25395,7 +25372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="307" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>18</v>
       </c>
@@ -25448,7 +25425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="308" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>18</v>
       </c>
@@ -25501,7 +25478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="309" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>18</v>
       </c>
@@ -25554,7 +25531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="310" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>18</v>
       </c>
@@ -25607,7 +25584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>18</v>
       </c>
@@ -25660,7 +25637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="312" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>18</v>
       </c>
@@ -25713,7 +25690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>18</v>
       </c>
@@ -25766,7 +25743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>18</v>
       </c>
@@ -25819,7 +25796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="315" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>18</v>
       </c>
@@ -25872,7 +25849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>18</v>
       </c>
@@ -25925,7 +25902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>18</v>
       </c>
@@ -25978,7 +25955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="318" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>18</v>
       </c>
@@ -26031,7 +26008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>18</v>
       </c>
@@ -26084,7 +26061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>18</v>
       </c>
@@ -26137,7 +26114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>18</v>
       </c>
@@ -26190,7 +26167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>18</v>
       </c>
@@ -26243,7 +26220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="323" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>18</v>
       </c>
@@ -26296,7 +26273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>18</v>
       </c>
@@ -26349,7 +26326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>18</v>
       </c>
@@ -26402,7 +26379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>18</v>
       </c>
@@ -26455,7 +26432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>18</v>
       </c>
@@ -26508,7 +26485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="328" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>18</v>
       </c>
@@ -26561,7 +26538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>18</v>
       </c>
@@ -26614,7 +26591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>18</v>
       </c>
@@ -26667,7 +26644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>18</v>
       </c>
@@ -26720,7 +26697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="332" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>18</v>
       </c>
@@ -26773,7 +26750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>18</v>
       </c>
@@ -26826,7 +26803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="334" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>18</v>
       </c>
@@ -26879,7 +26856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>18</v>
       </c>
@@ -26932,7 +26909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>18</v>
       </c>
@@ -26985,7 +26962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>18</v>
       </c>
@@ -27038,7 +27015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="338" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>18</v>
       </c>
@@ -27091,7 +27068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>18</v>
       </c>
@@ -27144,7 +27121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="340" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>18</v>
       </c>
@@ -27197,7 +27174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="341" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>18</v>
       </c>
@@ -27250,7 +27227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="342" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>18</v>
       </c>
@@ -27303,7 +27280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="343" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>18</v>
       </c>
@@ -27356,7 +27333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="344" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>18</v>
       </c>
@@ -27409,7 +27386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="345" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>18</v>
       </c>
@@ -27462,7 +27439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="346" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>18</v>
       </c>
@@ -27515,7 +27492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="347" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>18</v>
       </c>
@@ -27568,7 +27545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="348" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>18</v>
       </c>
@@ -27621,7 +27598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="349" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>18</v>
       </c>
@@ -27674,7 +27651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="350" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>18</v>
       </c>
@@ -27727,7 +27704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>18</v>
       </c>
@@ -27780,7 +27757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="352" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>18</v>
       </c>
@@ -27833,7 +27810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="353" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>18</v>
       </c>
@@ -27886,7 +27863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="354" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>18</v>
       </c>
@@ -27939,7 +27916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="355" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>18</v>
       </c>
@@ -27992,7 +27969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="356" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>18</v>
       </c>
@@ -28045,7 +28022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="357" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>18</v>
       </c>
@@ -28098,7 +28075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="358" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>18</v>
       </c>
@@ -28151,7 +28128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="359" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>18</v>
       </c>
@@ -28204,7 +28181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="360" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>18</v>
       </c>
@@ -28257,7 +28234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="361" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>18</v>
       </c>
@@ -28310,7 +28287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="362" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>18</v>
       </c>
@@ -28363,7 +28340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="363" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>18</v>
       </c>
@@ -28416,7 +28393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="364" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>18</v>
       </c>
@@ -28469,7 +28446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="365" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>18</v>
       </c>
@@ -28522,7 +28499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="366" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A366" s="8" t="s">
         <v>18</v>
       </c>
@@ -28575,7 +28552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A367" s="8" t="s">
         <v>18</v>
       </c>
@@ -28628,7 +28605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A368" s="8" t="s">
         <v>18</v>
       </c>
@@ -28681,7 +28658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A369" s="8" t="s">
         <v>18</v>
       </c>
@@ -28734,7 +28711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A370" s="8" t="s">
         <v>18</v>
       </c>
@@ -28787,7 +28764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A371" s="8" t="s">
         <v>18</v>
       </c>
@@ -28828,7 +28805,7 @@
         <v>56</v>
       </c>
       <c r="N371" s="12" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="O371" s="8" t="s">
         <v>34</v>
@@ -28840,7 +28817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A372" s="8" t="s">
         <v>18</v>
       </c>
@@ -28881,7 +28858,7 @@
         <v>56</v>
       </c>
       <c r="N372" s="12" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="O372" s="8" t="s">
         <v>34</v>
@@ -28893,7 +28870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A373" s="8" t="s">
         <v>18</v>
       </c>
@@ -28947,7 +28924,7 @@
       </c>
       <c r="U373" s="7"/>
     </row>
-    <row r="374" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A374" s="8" t="s">
         <v>18</v>
       </c>
@@ -29001,7 +28978,7 @@
       </c>
       <c r="U374" s="7"/>
     </row>
-    <row r="375" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A375" s="8" t="s">
         <v>18</v>
       </c>
@@ -29054,7 +29031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A376" s="8" t="s">
         <v>18</v>
       </c>
@@ -29107,7 +29084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A377" s="8" t="s">
         <v>18</v>
       </c>
@@ -29160,7 +29137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A378" s="8" t="s">
         <v>18</v>
       </c>
@@ -29213,7 +29190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:21" x14ac:dyDescent="0.3">
       <c r="H379" s="1"/>
       <c r="K379" s="2"/>
       <c r="L379" s="2"/>
